--- a/reports/pdf_rolling5_20260722.xlsx
+++ b/reports/pdf_rolling5_20260722.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,237억   ·   현금 129억(3.0%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 18종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>238</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>7909216000</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-71</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-2549638400</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>229</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>871189280</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-2525731200</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>2642688000</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-904227840</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -801,8 +813,10 @@
       <c r="B9" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>992634880</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-50</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-610080000</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -845,8 +861,10 @@
       <c r="B10" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>481129920</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-45</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-1283400000</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -889,8 +909,10 @@
       <c r="B11" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>2295686400</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -910,8 +932,10 @@
       <c r="H11" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-767808000</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>435309440</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -954,8 +980,10 @@
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-447570560</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -977,8 +1005,10 @@
       <c r="B13" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>2540313600</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -998,8 +1028,10 @@
       <c r="H13" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-1605254400</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1021,8 +1053,10 @@
       <c r="B14" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>4285440000</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-4602483200</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>684480000</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-26</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-419120000</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1109,8 +1149,10 @@
       <c r="B16" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>851136000</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1130,8 +1172,10 @@
       <c r="H16" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-460486400</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1153,8 +1197,10 @@
       <c r="B17" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>807091200</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1174,8 +1220,10 @@
       <c r="H17" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>-415152000</v>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,132 +1239,144 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>404140800</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.62%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I18" s="15" t="n">
-        <v>-418723200</v>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.90%</t>
+          <t>0.37%→0.25%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>1201113600</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>3.95%→4.24%</t>
+          <t>0.51%→0.62%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>-359004800</v>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.25%</t>
+          <t>0.58%→0.46%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>423782400</v>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>3.95%→4.24%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I20" s="15" t="n">
-        <v>-393030400</v>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>0.91%→0.90%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1329,8 +1389,10 @@
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>843200000</v>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1350,8 +1412,10 @@
       <c r="H21" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I21" s="15" t="n">
-        <v>-383904000</v>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1373,8 +1437,10 @@
       <c r="B22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>746976000</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1394,8 +1460,10 @@
       <c r="H22" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>-921369600</v>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1417,8 +1485,10 @@
       <c r="B23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>424377600</v>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1438,8 +1508,10 @@
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I23" s="15" t="n">
-        <v>-1035350400</v>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1466,8 +1538,10 @@
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I24" s="15" t="n">
-        <v>-412473600</v>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1494,8 +1568,10 @@
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I25" s="15" t="n">
-        <v>-649958400</v>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1522,8 +1598,10 @@
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I26" s="15" t="n">
-        <v>-363072000</v>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1539,7 +1617,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,823억   ·   현금 29억(0.8%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1634,8 +1712,10 @@
       <c r="B31" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>1855299600</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1655,8 +1735,10 @@
       <c r="H31" s="15" t="n">
         <v>-138</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-7517577600</v>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1678,8 +1760,10 @@
       <c r="B32" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>1120932000</v>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1706,8 +1790,10 @@
       <c r="B33" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>1080424800</v>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1734,8 +1820,10 @@
       <c r="B34" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>1906632000</v>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1762,8 +1850,10 @@
       <c r="B35" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>1083975000</v>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1784,7 +1874,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,434억   ·   현금 94억(3.7%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1879,8 +1969,10 @@
       <c r="B40" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>3700125000</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1900,8 +1992,10 @@
       <c r="H40" s="15" t="n">
         <v>-452</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-11305650000</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1923,8 +2017,10 @@
       <c r="B41" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>2820030000</v>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1944,8 +2040,10 @@
       <c r="H41" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I41" s="15" t="n">
-        <v>-2228700000</v>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1967,8 +2065,10 @@
       <c r="B42" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>4251573000</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1988,8 +2088,10 @@
       <c r="H42" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I42" s="15" t="n">
-        <v>-3579030000</v>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2011,8 +2113,10 @@
       <c r="B43" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>3268944000</v>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2039,8 +2143,10 @@
       <c r="B44" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>2286660000</v>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2061,7 +2167,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,246억   ·   현금 55억(2.4%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2085,7 +2191,7 @@
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -1억      오늘 2026-07-22  vs  5일전 2026-07-14      매수 10종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B49" s="4" t="n"/>
@@ -2180,12 +2286,14 @@
       <c r="B52" s="11" t="n">
         <v>485</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>135557500</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.43%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2201,12 +2309,14 @@
       <c r="H52" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-40926540</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2224,12 +2334,14 @@
       <c r="B53" s="11" t="n">
         <v>201</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>129990720</v>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>6.64%→6.98%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2245,12 +2357,14 @@
       <c r="H53" s="15" t="n">
         <v>-108</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-60186240</v>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.82%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2268,12 +2382,14 @@
       <c r="B54" s="11" t="n">
         <v>113</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>278906600</v>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>5.47%→6.29%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2289,12 +2405,14 @@
       <c r="H54" s="15" t="n">
         <v>-73</v>
       </c>
-      <c r="I54" s="15" t="n">
-        <v>-85129680</v>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.28%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2312,12 +2430,14 @@
       <c r="B55" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>132818400</v>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.07%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2333,12 +2453,14 @@
       <c r="H55" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I55" s="15" t="n">
-        <v>-17881980</v>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2356,12 +2478,14 @@
       <c r="B56" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>118628400</v>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.73%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2377,12 +2501,14 @@
       <c r="H56" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I56" s="15" t="n">
-        <v>-79876800</v>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.51%→1.24%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2400,12 +2526,14 @@
       <c r="B57" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>107018400</v>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>7.14%→7.40%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2421,12 +2549,14 @@
       <c r="H57" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I57" s="15" t="n">
-        <v>-76884000</v>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.02%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2444,12 +2574,14 @@
       <c r="B58" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>62350000</v>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.70%→2.86%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2459,23 +2591,25 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I58" s="15" t="n">
-        <v>-132199200</v>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.09%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2622,14 @@
       <c r="B59" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>86223600</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.24%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2503,23 +2639,25 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I59" s="15" t="n">
-        <v>-71982000</v>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>3.81%→3.55%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2670,14 @@
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>51342000</v>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2553,12 +2693,14 @@
       <c r="H60" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>-88855200</v>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2576,12 +2718,14 @@
       <c r="B61" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>33325000</v>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.11%→0.21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2597,12 +2741,14 @@
       <c r="H61" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I61" s="15" t="n">
-        <v>-77176400</v>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.29%→3.02%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2625,12 +2771,14 @@
       <c r="H62" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I62" s="15" t="n">
-        <v>-61490000</v>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.41%→1.20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2653,12 +2801,14 @@
       <c r="H63" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I63" s="15" t="n">
-        <v>-39594400</v>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.93%→2.77%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2670,7 +2820,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 1억(0.2%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>
@@ -2765,8 +2915,10 @@
       <c r="B68" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>362244800</v>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2786,8 +2938,10 @@
       <c r="H68" s="15" t="n">
         <v>-93</v>
       </c>
-      <c r="I68" s="15" t="n">
-        <v>-462805200</v>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2809,8 +2963,10 @@
       <c r="B69" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>756412800</v>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -2830,8 +2986,10 @@
       <c r="H69" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I69" s="15" t="n">
-        <v>-257241600</v>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -2853,8 +3011,10 @@
       <c r="B70" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>1426104000</v>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2874,8 +3034,10 @@
       <c r="H70" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I70" s="15" t="n">
-        <v>-238867200</v>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260722.xlsx
+++ b/reports/pdf_rolling5_20260722.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 18종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,306억   ·   현금 129억(3.0%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,10 +669,8 @@
       <c r="B6" s="11" t="n">
         <v>238</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>7869351000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -692,10 +690,8 @@
       <c r="H6" s="15" t="n">
         <v>-71</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-2536787400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -717,10 +713,8 @@
       <c r="B7" s="11" t="n">
         <v>229</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>866798205</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,20 +728,18 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍  (편출)</t>
+          <t>엠케이전자  (편출)</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-899670240</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.55%→0.00%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -765,10 +757,8 @@
       <c r="B8" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>2629368000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -782,20 +772,18 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>엠케이전자  (편출)</t>
+          <t>에스앤에스텍  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-2513000700</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>0.55%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -813,10 +801,8 @@
       <c r="B9" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>987631680</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -836,10 +822,8 @@
       <c r="H9" s="15" t="n">
         <v>-50</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-607005000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -861,10 +845,8 @@
       <c r="B10" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>478704870</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -884,10 +866,8 @@
       <c r="H10" s="15" t="n">
         <v>-45</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-1276931250</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -909,10 +889,8 @@
       <c r="B11" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>2284115400</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -932,10 +910,8 @@
       <c r="H11" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-763938000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -957,10 +933,8 @@
       <c r="B12" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>433115340</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -980,10 +954,8 @@
       <c r="H12" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-445314660</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1005,10 +977,8 @@
       <c r="B13" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>2527509600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1028,10 +998,8 @@
       <c r="H13" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-1597163400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1053,10 +1021,8 @@
       <c r="B14" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>4263840000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1076,10 +1042,8 @@
       <c r="H14" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-4579285200</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1101,10 +1065,8 @@
       <c r="B15" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>681030000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1124,10 +1086,8 @@
       <c r="H15" s="15" t="n">
         <v>-26</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-417007500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1149,10 +1109,8 @@
       <c r="B16" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="11" t="n">
+        <v>846846000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1172,10 +1130,8 @@
       <c r="H16" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-458165400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1197,10 +1153,8 @@
       <c r="B17" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="11" t="n">
+        <v>803023200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1220,10 +1174,8 @@
       <c r="H17" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="15" t="n">
+        <v>-413059500</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1239,25 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C18" s="11" t="n">
+        <v>402103800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>0.51%→0.62%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1268,10 +1218,8 @@
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="15" t="n">
+        <v>-357195300</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1287,96 +1235,88 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C19" s="11" t="n">
+        <v>1195059600</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.62%</t>
+          <t>3.95%→4.24%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="15" t="n">
+        <v>-416612700</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>0.91%→0.90%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="11" t="n">
+        <v>421646400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>3.95%→4.24%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="15" t="n">
+        <v>-391049400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.90%</t>
+          <t>0.58%→0.46%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1389,10 +1329,8 @@
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="11" t="n">
+        <v>838950000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1412,10 +1350,8 @@
       <c r="H21" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="15" t="n">
+        <v>-381969000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1431,25 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="11" t="n">
+        <v>422238600</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.58%</t>
+          <t>1.27%→1.30%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>41→44</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1460,10 +1394,8 @@
       <c r="H22" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="15" t="n">
+        <v>-916725600</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1479,25 +1411,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="11" t="n">
+        <v>743211000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.30%</t>
+          <t>2.23%→2.58%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>41→44</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -1508,10 +1438,8 @@
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="15" t="n">
+        <v>-1030131900</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1532,25 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="15" t="n">
+        <v>-646682400</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>2.37%→2.14%</t>
+          <t>1.88%→1.58%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>68→62</t>
         </is>
       </c>
     </row>
@@ -1562,25 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="15" t="n">
+        <v>-361242000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.88%→1.58%</t>
+          <t>1.34%→1.05%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>68→62</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1592,32 +1516,30 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="15" t="n">
+        <v>-410394600</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.05%</t>
+          <t>2.37%→2.14%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,742억   ·   현금 29억(0.8%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1712,10 +1634,8 @@
       <c r="B31" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="11" t="n">
+        <v>1848924000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1735,10 +1655,8 @@
       <c r="H31" s="15" t="n">
         <v>-138</v>
       </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="15" t="n">
+        <v>-7491744000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1760,10 +1678,8 @@
       <c r="B32" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C32" s="11" t="n">
+        <v>1117080000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1790,10 +1706,8 @@
       <c r="B33" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C33" s="11" t="n">
+        <v>1076712000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1820,10 +1734,8 @@
       <c r="B34" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="11" t="n">
+        <v>1900080000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1850,10 +1762,8 @@
       <c r="B35" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="11" t="n">
+        <v>1080250000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1784,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,467억   ·   현금 94억(3.7%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1969,10 +1879,8 @@
       <c r="B40" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="11" t="n">
+        <v>3684037500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1992,10 +1900,8 @@
       <c r="H40" s="15" t="n">
         <v>-452</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="15" t="n">
+        <v>-11256495000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -2017,10 +1923,8 @@
       <c r="B41" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="11" t="n">
+        <v>2807769000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -2034,25 +1938,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="15" t="n">
+        <v>-3563469000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>3.74%→2.91%</t>
+          <t>3.98%→2.34%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>79→60</t>
+          <t>49→30</t>
         </is>
       </c>
     </row>
@@ -2065,10 +1967,8 @@
       <c r="B42" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="11" t="n">
+        <v>4233087900</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2082,25 +1982,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="15" t="n">
+        <v>-2219010000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>3.98%→2.34%</t>
+          <t>3.74%→2.91%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>49→30</t>
+          <t>79→60</t>
         </is>
       </c>
     </row>
@@ -2113,10 +2011,8 @@
       <c r="B43" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="11" t="n">
+        <v>3254731200</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2143,10 +2039,8 @@
       <c r="B44" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="11" t="n">
+        <v>2276718000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2167,7 +2061,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,226억   ·   현금 53억(2.4%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2191,7 +2085,7 @@
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 10종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -1억(-0.2%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B49" s="4" t="n"/>
@@ -2286,14 +2180,12 @@
       <c r="B52" s="11" t="n">
         <v>485</v>
       </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="11" t="n">
+        <v>119795000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.00%→0.43%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2309,14 +2201,12 @@
       <c r="H52" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="15" t="n">
+        <v>-36167640</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.45%→0.32%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2334,14 +2224,12 @@
       <c r="B53" s="11" t="n">
         <v>201</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="11" t="n">
+        <v>114875520</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.64%→6.98%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2357,14 +2245,12 @@
       <c r="H53" s="15" t="n">
         <v>-108</v>
       </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="15" t="n">
+        <v>-53187840</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.02%→0.82%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2382,14 +2268,12 @@
       <c r="B54" s="11" t="n">
         <v>113</v>
       </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="11" t="n">
+        <v>246475600</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.47%→6.29%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2405,14 +2289,12 @@
       <c r="H54" s="15" t="n">
         <v>-73</v>
       </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="15" t="n">
+        <v>-75230880</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.56%→1.28%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2430,14 +2312,12 @@
       <c r="B55" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C55" s="11" t="n">
+        <v>117374400</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.68%→3.07%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2453,14 +2333,12 @@
       <c r="H55" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="15" t="n">
+        <v>-15802680</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.36%→0.30%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2478,14 +2356,12 @@
       <c r="B56" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="11" t="n">
+        <v>104834400</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.38%→2.73%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2501,14 +2377,12 @@
       <c r="H56" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="15" t="n">
+        <v>-70588800</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.51%→1.24%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2526,14 +2400,12 @@
       <c r="B57" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="11" t="n">
+        <v>94574400</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.14%→7.40%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2549,14 +2421,12 @@
       <c r="H57" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="15" t="n">
+        <v>-67944000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.27%→1.02%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2574,14 +2444,12 @@
       <c r="B58" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="11" t="n">
+        <v>55100000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.70%→2.86%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2591,25 +2459,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="15" t="n">
+        <v>-78523200</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2622,14 +2488,12 @@
       <c r="B59" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="11" t="n">
+        <v>76197600</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.99%→2.24%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2639,25 +2503,23 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="15" t="n">
+        <v>-63612000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.81%→3.55%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
@@ -2670,14 +2532,12 @@
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="11" t="n">
+        <v>45372000</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.99%→2.13%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2687,25 +2547,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="15" t="n">
+        <v>-116827200</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.55%→3.09%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2718,14 +2576,12 @@
       <c r="B61" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="11" t="n">
+        <v>29450000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11%→0.21%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2741,14 +2597,12 @@
       <c r="H61" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="15" t="n">
+        <v>-68202400</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.29%→3.02%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2771,14 +2625,12 @@
       <c r="H62" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="15" t="n">
+        <v>-54340000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.41%→1.20%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2801,14 +2653,12 @@
       <c r="H63" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="15" t="n">
+        <v>-34990400</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.93%→2.77%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2820,7 +2670,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 469억   ·   현금 1억(0.2%)      오늘 2026-07-22  vs  5일전 2026-07-14      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>
@@ -2915,10 +2765,8 @@
       <c r="B68" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="11" t="n">
+        <v>349753600</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2938,10 +2786,8 @@
       <c r="H68" s="15" t="n">
         <v>-93</v>
       </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="15" t="n">
+        <v>-446846400</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2963,10 +2809,8 @@
       <c r="B69" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="11" t="n">
+        <v>730329600</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -2986,10 +2830,8 @@
       <c r="H69" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="15" t="n">
+        <v>-248371200</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -3011,10 +2853,8 @@
       <c r="B70" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="11" t="n">
+        <v>1376928000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -3034,10 +2874,8 @@
       <c r="H70" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="15" t="n">
+        <v>-230630400</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260722.xlsx
+++ b/reports/pdf_rolling5_20260722.xlsx
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-646682400</v>
+        <v>-361242000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.88%→1.58%</t>
+          <t>1.34%→1.05%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>68→62</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-361242000</v>
+        <v>-646682400</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.05%</t>
+          <t>1.88%→1.58%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>68→62</t>
         </is>
       </c>
     </row>
@@ -1938,23 +1938,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-3563469000</v>
+        <v>-2219010000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>3.98%→2.34%</t>
+          <t>3.74%→2.91%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>49→30</t>
+          <t>79→60</t>
         </is>
       </c>
     </row>
@@ -1982,23 +1982,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2219010000</v>
+        <v>-3563469000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>3.74%→2.91%</t>
+          <t>3.98%→2.34%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>79→60</t>
+          <t>49→30</t>
         </is>
       </c>
     </row>
@@ -2181,11 +2181,11 @@
         <v>485</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>119795000</v>
+        <v>126429800</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.43%</t>
+          <t>0.00%→0.45%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2202,7 +2202,7 @@
         <v>-174</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-36167640</v>
+        <v>-36233760</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2225,11 +2225,11 @@
         <v>201</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>114875520</v>
+        <v>113500680</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>6.64%→6.98%</t>
+          <t>6.56%→6.90%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2246,11 +2246,11 @@
         <v>-108</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-53187840</v>
+        <v>-53023680</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.82%</t>
+          <t>1.01%→0.81%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2269,11 +2269,11 @@
         <v>113</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>246475600</v>
+        <v>240034600</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>5.47%→6.29%</t>
+          <t>5.33%→6.13%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2290,11 +2290,11 @@
         <v>-73</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-75230880</v>
+        <v>-78171320</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.28%</t>
+          <t>1.63%→1.33%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2313,11 +2313,11 @@
         <v>78</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>117374400</v>
+        <v>123006000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.07%</t>
+          <t>2.81%→3.22%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2334,11 +2334,11 @@
         <v>-29</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-15802680</v>
+        <v>-16309600</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.30%</t>
+          <t>0.37%→0.31%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2357,7 +2357,7 @@
         <v>38</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>104834400</v>
+        <v>104690000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2378,11 +2378,11 @@
         <v>-18</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-70588800</v>
+        <v>-75376800</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.51%→1.24%</t>
+          <t>1.61%→1.33%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2401,11 +2401,11 @@
         <v>34</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>94574400</v>
+        <v>93540800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>7.14%→7.40%</t>
+          <t>7.07%→7.33%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2422,11 +2422,11 @@
         <v>-10</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-67944000</v>
+        <v>-67488000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.02%</t>
+          <t>1.26%→1.01%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2445,11 +2445,11 @@
         <v>25</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>55100000</v>
+        <v>54625000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.70%→2.86%</t>
+          <t>2.67%→2.84%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2459,23 +2459,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>올릭스  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-78523200</v>
+        <v>-113338800</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>3.44%→3.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2489,11 +2489,11 @@
         <v>18</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>76197600</v>
+        <v>76334400</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.24%</t>
+          <t>2.00%→2.25%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2510,11 +2510,11 @@
         <v>-9</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-63612000</v>
+        <v>-61081200</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>3.81%→3.55%</t>
+          <t>3.66%→3.41%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2533,11 +2533,11 @@
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>45372000</v>
+        <v>46010400</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.13%</t>
+          <t>2.01%→2.16%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>올릭스  (편출)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-116827200</v>
+        <v>-74692800</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.09%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2577,11 +2577,11 @@
         <v>5</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>29450000</v>
+        <v>30780000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.11%→0.21%</t>
+          <t>0.11%→0.22%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2598,11 +2598,11 @@
         <v>-7</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-68202400</v>
+        <v>-71820000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.29%→3.02%</t>
+          <t>3.47%→3.18%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2626,11 +2626,11 @@
         <v>-5</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-54340000</v>
+        <v>-54188000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.41%→1.20%</t>
+          <t>1.40%→1.20%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2654,11 +2654,11 @@
         <v>-4</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-34990400</v>
+        <v>-35294400</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.93%→2.77%</t>
+          <t>2.95%→2.80%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
